--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.91108010591737</v>
+        <v>9.898050517211573</v>
       </c>
       <c r="D2" t="n">
-        <v>60.9247870185869</v>
+        <v>9.900277890520371</v>
       </c>
       <c r="E2" t="n">
-        <v>12.80550961452879</v>
+        <v>2.080895312360929</v>
       </c>
       <c r="F2" t="n">
-        <v>12.77132845922048</v>
+        <v>2.075340874623328</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.3146729729722</v>
+        <v>6.388634358107983</v>
       </c>
       <c r="D3" t="n">
-        <v>39.33122258062416</v>
+        <v>6.391323669351426</v>
       </c>
       <c r="E3" t="n">
-        <v>12.80550961452879</v>
+        <v>2.080895312360929</v>
       </c>
       <c r="F3" t="n">
-        <v>12.77132845922048</v>
+        <v>2.075340874623328</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.30757275498862</v>
+        <v>8.337480572685651</v>
       </c>
       <c r="D4" t="n">
-        <v>51.24999130245039</v>
+        <v>8.328123586648189</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80550961452879</v>
+        <v>2.080895312360929</v>
       </c>
       <c r="F4" t="n">
-        <v>12.77132845922048</v>
+        <v>2.075340874623328</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.49412879425893</v>
+        <v>4.792795929067077</v>
       </c>
       <c r="D5" t="n">
-        <v>29.06423152164764</v>
+        <v>4.722937622267741</v>
       </c>
       <c r="E5" t="n">
-        <v>12.80550961452879</v>
+        <v>2.080895312360929</v>
       </c>
       <c r="F5" t="n">
-        <v>12.77132845922048</v>
+        <v>2.075340874623328</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.42198319968016</v>
+        <v>4.456072269948026</v>
       </c>
       <c r="D6" t="n">
-        <v>27.93534824242665</v>
+        <v>4.539494089394331</v>
       </c>
       <c r="E6" t="n">
-        <v>12.80550961452879</v>
+        <v>2.080895312360929</v>
       </c>
       <c r="F6" t="n">
-        <v>12.77132845922048</v>
+        <v>2.075340874623328</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
